--- a/dashboard_xbox_gustavo.xlsx
+++ b/dashboard_xbox_gustavo.xlsx
@@ -1958,11 +1958,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="182"/>
-        <c:axId val="66250752"/>
-        <c:axId val="66255648"/>
+        <c:axId val="1392546464"/>
+        <c:axId val="1392558432"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="66250752"/>
+        <c:axId val="1392546464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2005,7 +2005,7 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66255648"/>
+        <c:crossAx val="1392558432"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2013,7 +2013,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66255648"/>
+        <c:axId val="1392558432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2023,7 +2023,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="66250752"/>
+        <c:crossAx val="1392546464"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2510,11 +2510,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="182"/>
-        <c:axId val="66258368"/>
-        <c:axId val="66257280"/>
+        <c:axId val="1392547008"/>
+        <c:axId val="1392549184"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="66258368"/>
+        <c:axId val="1392547008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2557,7 +2557,7 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66257280"/>
+        <c:crossAx val="1392549184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2565,7 +2565,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66257280"/>
+        <c:axId val="1392549184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2575,7 +2575,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="66258368"/>
+        <c:crossAx val="1392547008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
